--- a/physician_forms/017_provider_approval_form--physician_forms.xlsx
+++ b/physician_forms/017_provider_approval_form--physician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1010,8 +1010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'hospital'}</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Hospital'}</t>
+          <t>Hospital</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'clinic'}</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Clinic'}</t>
+          <t>Clinic</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'jim'}</t>
+          <t>jim</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Jim'}</t>
+          <t>Jim</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'bob'}</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Bob'}</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'In progress'}</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'jim'}</t>
+          <t>jim</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Jim'}</t>
+          <t>Jim</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'bob'}</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Bob'}</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
